--- a/www/download/IND.gross_output.s.mv.rpA2.xlsx
+++ b/www/download/IND.gross_output.s.mv.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>36958.591</t>
+          <t>36958590626.6968</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>38107.204</t>
+          <t>38107203869.5149</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>38325.665</t>
+          <t>38325665004.4621</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38709.92</t>
+          <t>38709919516.0742</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41453.449</t>
+          <t>41453449470.3051</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>40920.608</t>
+          <t>40920607752.2924</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40235.429</t>
+          <t>40235429031.1802</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42914.707</t>
+          <t>42914707363.4471</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>45352.93</t>
+          <t>45352930062.1066</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50428.455</t>
+          <t>50428455010.3724</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>52082.754</t>
+          <t>52082753561.4882</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>53302.197</t>
+          <t>53302197239.875</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>56102.375</t>
+          <t>56102374921.28</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>59267.516</t>
+          <t>59267515833.0959</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>61165.142</t>
+          <t>61165141665.2918</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21848.41</t>
+          <t>21848409520.1338</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22667.778</t>
+          <t>22667778024.5426</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21505.268</t>
+          <t>21505268224.8203</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22061.402</t>
+          <t>22061401948.5548</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22486.84</t>
+          <t>22486840393.564</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>23515.746</t>
+          <t>23515746380.8706</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24275.327</t>
+          <t>24275326772.0424</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24137.208</t>
+          <t>24137208390.6859</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24829.989</t>
+          <t>24829989087.8783</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26454.945</t>
+          <t>26454945259.0143</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>26181.867</t>
+          <t>26181867001.87</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>27962.368</t>
+          <t>27962368395.5734</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>28717.03</t>
+          <t>28717029609.7528</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>26832.61</t>
+          <t>26832610295.1922</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>23707.583</t>
+          <t>23707582710.9602</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24806.296</t>
+          <t>24806295937.3893</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23790.741</t>
+          <t>23790740807.3766</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22706.357</t>
+          <t>22706357263.177</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23203.028</t>
+          <t>23203027572.9715</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23900.653</t>
+          <t>23900653321.9648</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>26163.874</t>
+          <t>26163873633.7901</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26299.052</t>
+          <t>26299052340.594</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25811.121</t>
+          <t>25811121412.6758</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27913.514</t>
+          <t>27913513659.1959</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30099.378</t>
+          <t>30099377862.5618</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>29435.863</t>
+          <t>29435862520.6249</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>31697.299</t>
+          <t>31697299437.7597</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>33103.554</t>
+          <t>33103553932.0101</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>38847.241</t>
+          <t>38847240678.4863</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>30166.197</t>
+          <t>30166197079.4224</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12326.54</t>
+          <t>12326539850.6948</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12883.094</t>
+          <t>12883093921.4433</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11422.291</t>
+          <t>11422290964.0526</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10675.851</t>
+          <t>10675851074.3865</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10658.671</t>
+          <t>10658671355.8747</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9625.326</t>
+          <t>9625326421.40617</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9060.138</t>
+          <t>9060137909.44518</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8948.561</t>
+          <t>8948560540.14797</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9537.963</t>
+          <t>9537963107.49033</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10469.786</t>
+          <t>10469786015.3212</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10647.815</t>
+          <t>10647814603.5723</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>11614.579</t>
+          <t>11614578644.606</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>12290.62</t>
+          <t>12290620121.1943</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>12866.855</t>
+          <t>12866854635.5175</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>12923.394</t>
+          <t>12923394241.9572</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>246012.537</t>
+          <t>246012536586.712</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>247352.576</t>
+          <t>247352575559.412</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>250239.145</t>
+          <t>250239144641.097</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>247947.695</t>
+          <t>247947694876.928</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>255990.085</t>
+          <t>255990085203.73</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>270756.362</t>
+          <t>270756362498.075</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>269842.469</t>
+          <t>269842468798.575</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>281113.089</t>
+          <t>281113089318.648</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>293683.244</t>
+          <t>293683243610.161</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>313037.059</t>
+          <t>313037059054.32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>324853.084</t>
+          <t>324853083647.284</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>332808.875</t>
+          <t>332808874680.622</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>349565.382</t>
+          <t>349565382208.736</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>370920.507</t>
+          <t>370920506554.364</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>365185.406</t>
+          <t>365185406085.193</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>69489.326</t>
+          <t>69489325900.7502</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71159.301</t>
+          <t>71159300859.4488</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71431.483</t>
+          <t>71431482844.16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72220.703</t>
+          <t>72220702549.7846</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>76046.561</t>
+          <t>76046561029.2463</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>83209.917</t>
+          <t>83209917185.555</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>83756.39</t>
+          <t>83756389878.6881</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>81528.269</t>
+          <t>81528268637.5876</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>84631.604</t>
+          <t>84631604399.0707</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>91692.925</t>
+          <t>91692925305.6114</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>94558.485</t>
+          <t>94558484683.1147</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>97653.082</t>
+          <t>97653081715.9027</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>95902.741</t>
+          <t>95902740713.3799</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>97694.989</t>
+          <t>97694988723.6861</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>91963.887</t>
+          <t>91963887320.6007</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2680931.49</t>
+          <t>2680931490388.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2794499.722</t>
+          <t>2794499722265</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2845312.384</t>
+          <t>2845312384165.02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2822416.229</t>
+          <t>2822416228764.86</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2818756.364</t>
+          <t>2818756364328.59</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2800346.178</t>
+          <t>2800346178398.1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2854753.452</t>
+          <t>2854753452057.54</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2912363.8</t>
+          <t>2912363800383.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3105882.429</t>
+          <t>3105882428991.1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3220383.738</t>
+          <t>3220383738209.9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3449874.065</t>
+          <t>3449874065307.67</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3878477.017</t>
+          <t>3878477016853.81</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4071301.174</t>
+          <t>4071301174322.89</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4320801.308</t>
+          <t>4320801307997.33</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4406132.331</t>
+          <t>4406132331201.64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1416.625</t>
+          <t>1416625018.05118</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1516.705</t>
+          <t>1516704646.71889</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1373.419</t>
+          <t>1373418645.71284</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1367.373</t>
+          <t>1367373491.87653</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1492.109</t>
+          <t>1492108629.86798</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1509.176</t>
+          <t>1509176082.37465</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1648.401</t>
+          <t>1648401355.44469</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1722.46</t>
+          <t>1722460286.38288</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1794.073</t>
+          <t>1794073035.19661</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1711.573</t>
+          <t>1711573249.92877</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1569.943</t>
+          <t>1569942835.48181</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1612.284</t>
+          <t>1612284220.94578</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1629.276</t>
+          <t>1629275708.99744</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2125.286</t>
+          <t>2125285852.13383</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1522.18</t>
+          <t>1522179610.59722</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>34365.604</t>
+          <t>34365603582.6948</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>35152.907</t>
+          <t>35152906600.4622</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35827.405</t>
+          <t>35827405304.8668</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>34508.132</t>
+          <t>34508132371.4104</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33370.158</t>
+          <t>33370158237.8005</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32189.394</t>
+          <t>32189394120.908</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32882.541</t>
+          <t>32882540770.0762</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33409.852</t>
+          <t>33409851943.7196</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33231.251</t>
+          <t>33231250678.439</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>34116.909</t>
+          <t>34116909315.8481</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>34495.338</t>
+          <t>34495338173.1882</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>36980.043</t>
+          <t>36980042861.6871</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>38104.677</t>
+          <t>38104677249.4284</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>37218.35</t>
+          <t>37218349794.1848</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>31855.993</t>
+          <t>31855992778.9914</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>217114.155</t>
+          <t>217114155249.432</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>202955.073</t>
+          <t>202955072855.684</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>193594.077</t>
+          <t>193594077457.872</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>203347.303</t>
+          <t>203347302830.098</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>206046.838</t>
+          <t>206046838351.455</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>215921.19</t>
+          <t>215921190355.215</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>208941.315</t>
+          <t>208941315272.587</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>205271.81</t>
+          <t>205271809618.251</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>218813.39</t>
+          <t>218813389779.73</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>228615.368</t>
+          <t>228615368076.517</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>225157.274</t>
+          <t>225157274336.421</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>235766.389</t>
+          <t>235766389053.453</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>246112.142</t>
+          <t>246112141785.387</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>225290.925</t>
+          <t>225290925384.694</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>195647.766</t>
+          <t>195647766136.699</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17027.117</t>
+          <t>17027117103.928</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17043.02</t>
+          <t>17043019531.3554</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18178.186</t>
+          <t>18178186349.0494</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16985.909</t>
+          <t>16985908731.4335</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16263.059</t>
+          <t>16263059225.9706</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16625.209</t>
+          <t>16625209036.4842</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17123.9</t>
+          <t>17123899809.9503</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17013.866</t>
+          <t>17013866198.3864</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18048.684</t>
+          <t>18048684353.5477</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18577.045</t>
+          <t>18577044829.3535</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18415.196</t>
+          <t>18415196454.1487</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>18938.855</t>
+          <t>18938855296.135</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>18827.473</t>
+          <t>18827473386.2678</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>18074.062</t>
+          <t>18074062275.4081</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>15821.519</t>
+          <t>15821518849.3864</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>68367.722</t>
+          <t>68367721831.2417</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>70862.045</t>
+          <t>70862045263.5745</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68953.141</t>
+          <t>68953140557.636</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>74488.49</t>
+          <t>74488489739.8851</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>81404.109</t>
+          <t>81404108699.9909</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>90019.587</t>
+          <t>90019586909.1146</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>92194.968</t>
+          <t>92194967825.3537</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>98291.462</t>
+          <t>98291461706.2124</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>102109.001</t>
+          <t>102109001121.555</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>108547.337</t>
+          <t>108547336851.038</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>115752.315</t>
+          <t>115752315444.921</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>122002.101</t>
+          <t>122002101379.514</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>125605.004</t>
+          <t>125605003933.685</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>120351.836</t>
+          <t>120351835902.19</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>99976.652</t>
+          <t>99976651604.6881</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4403.202</t>
+          <t>4403201540.65877</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4165.759</t>
+          <t>4165758614.53649</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4228.155</t>
+          <t>4228154550.70234</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4207.912</t>
+          <t>4207911822.64649</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3893.998</t>
+          <t>3893998041.95016</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4137.361</t>
+          <t>4137360587.15559</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4420.76</t>
+          <t>4420760194.4679</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4612.797</t>
+          <t>4612796530.12835</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4860.574</t>
+          <t>4860574297.39968</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5230.486</t>
+          <t>5230486118.37569</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4983.913</t>
+          <t>4983912994.46797</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>5088.119</t>
+          <t>5088119130.012</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4829.432</t>
+          <t>4829432221.40031</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4648.77</t>
+          <t>4648770041.29761</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3948.937</t>
+          <t>3948937438.1899</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17313.682</t>
+          <t>17313681818.2995</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17142.224</t>
+          <t>17142224463.388</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16987.145</t>
+          <t>16987144859.1492</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18034.328</t>
+          <t>18034328410.194</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19259.305</t>
+          <t>19259305463.2692</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19395.993</t>
+          <t>19395993235.8089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18942.428</t>
+          <t>18942428076.3436</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18924.541</t>
+          <t>18924540699.2898</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19690.965</t>
+          <t>19690965047.8883</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20363.108</t>
+          <t>20363107627.913</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>20941.774</t>
+          <t>20941774043.331</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>21870.212</t>
+          <t>21870212089.9916</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>22299.128</t>
+          <t>22299127818.0976</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>21227.091</t>
+          <t>21227091057.9506</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>16962.997</t>
+          <t>16962997003.3892</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>114471.832</t>
+          <t>114471832356.925</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>113931.353</t>
+          <t>113931353029.555</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>106497.81</t>
+          <t>106497809902.273</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>111068.375</t>
+          <t>111068374936.286</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>118700.911</t>
+          <t>118700910708.286</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>123248.468</t>
+          <t>123248468401.219</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>123695.997</t>
+          <t>123695997468.489</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>121285.392</t>
+          <t>121285391578.263</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>126051.944</t>
+          <t>126051943869.411</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>130921.017</t>
+          <t>130921017219.951</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>133973.801</t>
+          <t>133973801315.137</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>136647.249</t>
+          <t>136647249051.059</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>141795.926</t>
+          <t>141795926092.329</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>134609.586</t>
+          <t>134609585685.207</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>121910.275</t>
+          <t>121910274578.654</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>126751.778</t>
+          <t>126751777920.97</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>128929.404</t>
+          <t>128929403866.147</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>128273.391</t>
+          <t>128273390657.455</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>130434.161</t>
+          <t>130434160564.972</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>132034.773</t>
+          <t>132034772508.381</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>132942.871</t>
+          <t>132942871341.421</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>131766.862</t>
+          <t>131766861986.337</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>131728.567</t>
+          <t>131728566589.835</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>133452.157</t>
+          <t>133452156884.265</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>138317.316</t>
+          <t>138317315579.308</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>143220.7</t>
+          <t>143220699844.943</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>145657.615</t>
+          <t>145657615457.486</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>146697.466</t>
+          <t>146697466362.04</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>133727.29</t>
+          <t>133727290252.894</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>125086.435</t>
+          <t>125086435149.31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18436.966</t>
+          <t>18436966254.8641</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19268.125</t>
+          <t>19268125163.4703</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18004.069</t>
+          <t>18004068670.545</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18506.573</t>
+          <t>18506573498.7141</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18700.998</t>
+          <t>18700998357.8547</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20730.587</t>
+          <t>20730587372.4344</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19939.225</t>
+          <t>19939224920.3581</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20441.195</t>
+          <t>20441194990.6327</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20661.265</t>
+          <t>20661265201.0776</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>21231.748</t>
+          <t>21231747549.4286</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>21197.733</t>
+          <t>21197733467.465</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>23252.433</t>
+          <t>23252433087.8786</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>23562.652</t>
+          <t>23562651635.117</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>24100.664</t>
+          <t>24100663890.1799</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>22140.906</t>
+          <t>22140905502.0659</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26714.733</t>
+          <t>26714733139.8248</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26311.339</t>
+          <t>26311339360.5463</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25200.476</t>
+          <t>25200476201.8486</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25658.452</t>
+          <t>25658451576.9853</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>27964.648</t>
+          <t>27964647738.3522</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>27199.884</t>
+          <t>27199883844.3065</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>26558.87</t>
+          <t>26558870404.0675</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>26756.071</t>
+          <t>26756071028.3541</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>27128.845</t>
+          <t>27128845453.0554</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>26393.745</t>
+          <t>26393744551.7066</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>26156.141</t>
+          <t>26156140543.9443</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>26400.427</t>
+          <t>26400426596.952</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>26865.319</t>
+          <t>26865319127.57</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>24313.604</t>
+          <t>24313604007.1261</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>22630.531</t>
+          <t>22630530995.6614</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>187629.739</t>
+          <t>187629739458.974</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>199117.234</t>
+          <t>199117234389.225</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>197281.664</t>
+          <t>197281663950.128</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>185417.404</t>
+          <t>185417403703.01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>211496.68</t>
+          <t>211496679697.099</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>226805.268</t>
+          <t>226805267758.776</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>232070.071</t>
+          <t>232070070864.186</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>247442.031</t>
+          <t>247442031282.73</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>257561.086</t>
+          <t>257561085610.682</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>260904.846</t>
+          <t>260904845930.596</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>230634.411</t>
+          <t>230634411157.354</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>226602.75</t>
+          <t>226602750289.291</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>237055.383</t>
+          <t>237055383272.952</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>242534.833</t>
+          <t>242534833238.471</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>255486.124</t>
+          <t>255486123979.457</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1796076.976</t>
+          <t>1796076976309.1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1843399.446</t>
+          <t>1843399446139.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1897140.482</t>
+          <t>1897140482341.96</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1902867.802</t>
+          <t>1902867801600.94</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1877162.178</t>
+          <t>1877162178018.26</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1982097.202</t>
+          <t>1982097201845.85</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2086794.825</t>
+          <t>2086794825023.44</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2082738.135</t>
+          <t>2082738135048.01</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2262189.392</t>
+          <t>2262189391647.62</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2341640.539</t>
+          <t>2341640538804.4</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2387778.123</t>
+          <t>2387778122734.2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2410471.89</t>
+          <t>2410471890287.26</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2373243.278</t>
+          <t>2373243277715.16</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2368389.067</t>
+          <t>2368389066717.22</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2434101.991</t>
+          <t>2434101991129.53</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10094.805</t>
+          <t>10094805454.4852</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10575.497</t>
+          <t>10575497442.9686</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10476.617</t>
+          <t>10476616783.8028</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10608.812</t>
+          <t>10608812395.5349</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11786.541</t>
+          <t>11786540881.4265</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12556.439</t>
+          <t>12556439349.1927</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12926.862</t>
+          <t>12926861705.9664</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12549.997</t>
+          <t>12549997311.7512</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13565.446</t>
+          <t>13565445821.0382</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>14906.048</t>
+          <t>14906048076.7044</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15788.782</t>
+          <t>15788781701.5776</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>16610.493</t>
+          <t>16610493251.9308</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>17551.133</t>
+          <t>17551133431.8373</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>16196.068</t>
+          <t>16196068253.2238</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>15019.636</t>
+          <t>15019635678.5275</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>112336.373</t>
+          <t>112336373281.748</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>114170.09</t>
+          <t>114170089593.495</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>109808.528</t>
+          <t>109808528190.262</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>115216.684</t>
+          <t>115216684378.23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>119589.948</t>
+          <t>119589948130.09</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>128107.854</t>
+          <t>128107853749.218</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>126819.502</t>
+          <t>126819501574.663</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>127722.485</t>
+          <t>127722484637.155</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>135015.515</t>
+          <t>135015514827.961</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>141716.864</t>
+          <t>141716864184.47</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>142945.605</t>
+          <t>142945604987.336</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>155500.802</t>
+          <t>155500801594.037</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>157492.751</t>
+          <t>157492751259.794</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>143245.891</t>
+          <t>143245890847.205</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>118807.059</t>
+          <t>118807059258.08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>486961.012</t>
+          <t>486961012221.928</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>474231.768</t>
+          <t>474231768345.392</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>464386.198</t>
+          <t>464386198486.888</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>430875.5</t>
+          <t>430875499561.185</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>443444.695</t>
+          <t>443444695212.143</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>465698.264</t>
+          <t>465698264420.366</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>456301.843</t>
+          <t>456301842737.461</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>441150.724</t>
+          <t>441150724422.561</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>456708.662</t>
+          <t>456708661971.555</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>478111.746</t>
+          <t>478111746221.291</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>480322.869</t>
+          <t>480322868576.713</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>494629.857</t>
+          <t>494629856978.257</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>491659.499</t>
+          <t>491659498693.413</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>510624.054</t>
+          <t>510624054234.399</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>439070.105</t>
+          <t>439070105111.013</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>218966.372</t>
+          <t>218966371884.674</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>222724.723</t>
+          <t>222724722598.851</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>221669.257</t>
+          <t>221669257262.355</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>203001.263</t>
+          <t>203001262582.665</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>218892.916</t>
+          <t>218892915836.628</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>236042.393</t>
+          <t>236042392521.896</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>234785.56</t>
+          <t>234785559753.172</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>241530.851</t>
+          <t>241530850740.355</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>249313.145</t>
+          <t>249313144648.646</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>270280.248</t>
+          <t>270280248254.168</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>270220.09</t>
+          <t>270220089618.256</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>282115.306</t>
+          <t>282115305575.917</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>280068.215</t>
+          <t>280068215069.939</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>288789.73</t>
+          <t>288789729547.103</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>275732.822</t>
+          <t>275732821588.568</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9196.313</t>
+          <t>9196313298.72705</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8943.949</t>
+          <t>8943948544.96193</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8189.354</t>
+          <t>8189354061.08444</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8544.414</t>
+          <t>8544413843.22647</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8064.325</t>
+          <t>8064324575.74819</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8298.307</t>
+          <t>8298306593.52463</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8111.554</t>
+          <t>8111553986.41082</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8204.022</t>
+          <t>8204021989.45934</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8500.947</t>
+          <t>8500947288.46793</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8329.31</t>
+          <t>8329310317.05566</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8886.066</t>
+          <t>8886065633.26609</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8827.92</t>
+          <t>8827920477.60279</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9234.985</t>
+          <t>9234985356.04117</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9859.705</t>
+          <t>9859705307.29493</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8696.933</t>
+          <t>8696933409.22788</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1079.916</t>
+          <t>1079916123.34876</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>968.565</t>
+          <t>968564959.486977</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>934.566</t>
+          <t>934566135.452415</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1014.72</t>
+          <t>1014720433.81758</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>987.884</t>
+          <t>987884494.946037</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1063.722</t>
+          <t>1063721545.41091</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1035.094</t>
+          <t>1035093740.71143</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1045.768</t>
+          <t>1045768328.3726</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1131.84</t>
+          <t>1131839571.84372</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1352.34</t>
+          <t>1352340321.65789</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1395.042</t>
+          <t>1395041595.74093</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1424.742</t>
+          <t>1424742260.49558</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1460.595</t>
+          <t>1460594548.60381</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1506.038</t>
+          <t>1506037689.53875</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1496.053</t>
+          <t>1496052888.18843</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4486.87</t>
+          <t>4486869748.15086</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4351.855</t>
+          <t>4351855402.79717</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4341.393</t>
+          <t>4341392880.22357</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4339.361</t>
+          <t>4339360890.53858</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4155.768</t>
+          <t>4155767689.80101</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3779.426</t>
+          <t>3779426314.7461</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3729.563</t>
+          <t>3729563273.37533</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3719.731</t>
+          <t>3719731138.43712</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3967.375</t>
+          <t>3967375050.66683</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4332.982</t>
+          <t>4332981618.395</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4397.17</t>
+          <t>4397170067.33261</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4754.194</t>
+          <t>4754194253.70071</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5219.482</t>
+          <t>5219482091.13301</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4897.27</t>
+          <t>4897269972.84271</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3701.979</t>
+          <t>3701978937.11984</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>138280.818</t>
+          <t>138280817570.819</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>146026.581</t>
+          <t>146026581321.449</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>148962.436</t>
+          <t>148962435578.357</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>157876.083</t>
+          <t>157876082685.875</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>164495.211</t>
+          <t>164495210914.768</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>171969.211</t>
+          <t>171969210624.461</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>177649.907</t>
+          <t>177649907304.53</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>176837.961</t>
+          <t>176837960802.21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>179847.025</t>
+          <t>179847025355.162</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>190861.466</t>
+          <t>190861466416.876</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>200438.239</t>
+          <t>200438239376.644</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>200216.123</t>
+          <t>200216123175.096</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>199076.003</t>
+          <t>199076003219.907</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>212477.195</t>
+          <t>212477195468.931</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>205295.281</t>
+          <t>205295281209.604</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>589.626</t>
+          <t>589625657.536323</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>589.12</t>
+          <t>589120157.175958</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>500.998</t>
+          <t>500997603.092928</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>537.497</t>
+          <t>537497096.484977</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>619.498</t>
+          <t>619498452.973686</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>715.911</t>
+          <t>715911158.777118</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>585.596</t>
+          <t>585596397.57851</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>608.03</t>
+          <t>608029558.856201</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>639.942</t>
+          <t>639941872.813791</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>624.592</t>
+          <t>624592275.871377</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>594.731</t>
+          <t>594730638.488169</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>666.83</t>
+          <t>666829747.996617</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>666.827</t>
+          <t>666827406.686292</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>697.156</t>
+          <t>697156450.241556</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>620.933</t>
+          <t>620933246.188267</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>46750.469</t>
+          <t>46750469324.501</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>48305.433</t>
+          <t>48305433340.105</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>44990.721</t>
+          <t>44990721465.764</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>49416.768</t>
+          <t>49416767979.1906</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>52998.393</t>
+          <t>52998392797.624</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>51828.629</t>
+          <t>51828629340.2729</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>53787.048</t>
+          <t>53787047939.3463</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>47717.36</t>
+          <t>47717359768.611</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>57787.907</t>
+          <t>57787907061.5196</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>60112.192</t>
+          <t>60112191953.6322</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>62594.158</t>
+          <t>62594157567.1283</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>63157.214</t>
+          <t>63157213727.5472</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>66604.069</t>
+          <t>66604069495.8898</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>68480.389</t>
+          <t>68480389214.9932</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>60807.562</t>
+          <t>60807562194.8643</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>90003.533</t>
+          <t>90003533031.5729</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>91394.582</t>
+          <t>91394582124.9977</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>89535.309</t>
+          <t>89535309364.7072</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>89322.3</t>
+          <t>89322299948.5099</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>85825.928</t>
+          <t>85825928243.9657</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>86590.829</t>
+          <t>86590829196.2869</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>78209.769</t>
+          <t>78209769355.1684</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>74845.286</t>
+          <t>74845286249.5308</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>76377.219</t>
+          <t>76377218739.4546</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>79770.075</t>
+          <t>79770075204.6413</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>83329.892</t>
+          <t>83329891971.7114</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>87622.269</t>
+          <t>87622268825.6431</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>93473.531</t>
+          <t>93473530934.7986</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>93528.83</t>
+          <t>93528830483.6832</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>87265.671</t>
+          <t>87265670860.7326</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>19774.743</t>
+          <t>19774743464.7604</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19547.575</t>
+          <t>19547575201.7954</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18075.136</t>
+          <t>18075136114.9149</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>19102.583</t>
+          <t>19102583450.5464</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19301.532</t>
+          <t>19301532167.982</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>20913.239</t>
+          <t>20913239103.2617</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>21103.559</t>
+          <t>21103558689.2392</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20660.723</t>
+          <t>20660722568.5811</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>20950.107</t>
+          <t>20950106917.5042</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>22184.628</t>
+          <t>22184627574.5693</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>21638.264</t>
+          <t>21638263924.8307</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>22103.159</t>
+          <t>22103158885.9063</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>23119.551</t>
+          <t>23119551338.5716</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>24085.035</t>
+          <t>24085034921.5174</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>19322.89</t>
+          <t>19322890281.7273</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>39035.94</t>
+          <t>39035940403.6007</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>40652.922</t>
+          <t>40652922343.6869</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35421.678</t>
+          <t>35421677970.6287</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>32276.876</t>
+          <t>32276875904.3848</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>38522.561</t>
+          <t>38522560686.9584</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>37211.966</t>
+          <t>37211965582.7385</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>37386.31</t>
+          <t>37386309824.0792</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>34388.394</t>
+          <t>34388393603.7337</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>34972.908</t>
+          <t>34972907614.5233</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>34656.113</t>
+          <t>34656113457.7927</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>34546.152</t>
+          <t>34546151891.5791</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>35191.23</t>
+          <t>35191230397.185</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>36207.387</t>
+          <t>36207387251.6029</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>37229.119</t>
+          <t>37229118602.2318</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>35917.65</t>
+          <t>35917650235.3756</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>477450.536</t>
+          <t>477450535634.101</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>480635.558</t>
+          <t>480635557736.006</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>451966.617</t>
+          <t>451966617223.272</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>427062.161</t>
+          <t>427062160970.837</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>399766.005</t>
+          <t>399766004592.753</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>412991.737</t>
+          <t>412991737273.869</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>426457.552</t>
+          <t>426457551987.867</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>420042.536</t>
+          <t>420042535726.255</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>424440.277</t>
+          <t>424440277055.485</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>423028.839</t>
+          <t>423028839411.479</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>423120.546</t>
+          <t>423120545599.758</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>415879.92</t>
+          <t>415879919904.911</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>430728.768</t>
+          <t>430728768083.898</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>434733.205</t>
+          <t>434733204755.956</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>426417.112</t>
+          <t>426417112062.379</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13983.853</t>
+          <t>13983853362.5552</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14260.503</t>
+          <t>14260502686.4047</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13193.623</t>
+          <t>13193623056.9322</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12917.829</t>
+          <t>12917828876.409</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12416.863</t>
+          <t>12416863496.3987</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12204.93</t>
+          <t>12204930325.4562</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12365.721</t>
+          <t>12365721327.2823</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>11987.489</t>
+          <t>11987488691.8728</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>12360.525</t>
+          <t>12360525163.6691</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>12590.711</t>
+          <t>12590710920.4697</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>13179.558</t>
+          <t>13179558393.8795</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>13905.642</t>
+          <t>13905642307.0667</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>15343.643</t>
+          <t>15343642747.0696</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>15779.604</t>
+          <t>15779604395.9097</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>15162.285</t>
+          <t>15162285410.0688</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5839.508</t>
+          <t>5839508198.11613</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5683.532</t>
+          <t>5683531627.25694</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5351.093</t>
+          <t>5351092744.99548</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5420.224</t>
+          <t>5420223891.33928</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5518.582</t>
+          <t>5518581970.03752</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5783.041</t>
+          <t>5783040707.98232</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5671.646</t>
+          <t>5671645910.7369</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>5749.054</t>
+          <t>5749053622.65361</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>6167.08</t>
+          <t>6167080422.86422</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>6275.237</t>
+          <t>6275236509.27358</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>6277.316</t>
+          <t>6277315690.10473</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>6532.268</t>
+          <t>6532267784.20084</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>6853.088</t>
+          <t>6853087561.57858</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>7381.217</t>
+          <t>7381216538.66001</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>6551.368</t>
+          <t>6551368402.08151</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>24054.775</t>
+          <t>24054775114.0015</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>23564.398</t>
+          <t>23564398464.0508</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>22964.072</t>
+          <t>22964072362.3695</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>23919.147</t>
+          <t>23919147338.9746</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>24671.131</t>
+          <t>24671130529.2489</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>27062.005</t>
+          <t>27062004949.9025</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>26118.617</t>
+          <t>26118617057.464</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>25886.653</t>
+          <t>25886653382.3346</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>26901.664</t>
+          <t>26901663505.1958</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>27995.523</t>
+          <t>27995523174.3488</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>28808.874</t>
+          <t>28808874325.5366</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>29419.942</t>
+          <t>29419942225.2154</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>30886.832</t>
+          <t>30886832266.8449</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>28701.908</t>
+          <t>28701907948.4703</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>24707.681</t>
+          <t>24707680877.0162</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>76564.093</t>
+          <t>76564092881.7809</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>79531.698</t>
+          <t>79531697958.4364</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>84277.044</t>
+          <t>84277044082.2234</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>84061.256</t>
+          <t>84061255904.2412</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>86898.315</t>
+          <t>86898315477.0862</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>90543.161</t>
+          <t>90543161068.6546</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>86501.423</t>
+          <t>86501422912.517</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>88895.18</t>
+          <t>88895180267.0534</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>95425.408</t>
+          <t>95425407746.6453</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>100056.014</t>
+          <t>100056014485.738</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>104512.503</t>
+          <t>104512503276.352</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>105468.203</t>
+          <t>105468202863.7</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>107327.017</t>
+          <t>107327016969.66</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>113252.337</t>
+          <t>113252336590.268</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>98297.92</t>
+          <t>98297919601.1226</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>71079.213</t>
+          <t>71079212935.307</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>70539.949</t>
+          <t>70539949140.7279</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>70418.357</t>
+          <t>70418357204.1617</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69988.385</t>
+          <t>69988384676.9219</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>72040.422</t>
+          <t>72040421848.4827</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>78977.524</t>
+          <t>78977524393.0049</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>72786.438</t>
+          <t>72786438355.2868</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78121.921</t>
+          <t>78121920851.3308</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>82417.766</t>
+          <t>82417765649.4293</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>92187.075</t>
+          <t>92187074969.7731</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>91139.197</t>
+          <t>91139196862.9782</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>94411.867</t>
+          <t>94411867415.4034</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>95276.071</t>
+          <t>95276070816.3819</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>97026.99</t>
+          <t>97026989973.7792</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>83923.844</t>
+          <t>83923843741.9559</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>688904.487</t>
+          <t>688904487076.029</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>696677.023</t>
+          <t>696677023483.492</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>704925.972</t>
+          <t>704925971602.619</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>721066.183</t>
+          <t>721066183468.815</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>741618.571</t>
+          <t>741618570785.513</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>783652.956</t>
+          <t>783652956182.161</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>756836.35</t>
+          <t>756836349884.297</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>732297.768</t>
+          <t>732297767804.518</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>737335.527</t>
+          <t>737335527221.888</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>779488.088</t>
+          <t>779488087745.246</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>806016.86</t>
+          <t>806016860198.5</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>827003.985</t>
+          <t>827003984510.719</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>811145.798</t>
+          <t>811145797553.009</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>813774.405</t>
+          <t>813774404940.18</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>706030.255</t>
+          <t>706030254609.161</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4392360.07</t>
+          <t>4392360070136</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4561341.694</t>
+          <t>4561341693935.22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4749942.221</t>
+          <t>4749942221021.78</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4839934.033</t>
+          <t>4839934033440.72</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4868931.491</t>
+          <t>4868931491191.25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5091242.635</t>
+          <t>5091242635044.44</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5333214.032</t>
+          <t>5333214032018.04</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>5597698.898</t>
+          <t>5597698897946.12</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>5870188.949</t>
+          <t>5870188948961.68</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>6182071.405</t>
+          <t>6182071405396.57</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>6393496.831</t>
+          <t>6393496831371.4</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>6713239.614</t>
+          <t>6713239614048.22</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6791428.813</t>
+          <t>6791428812880.71</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>7005336.647</t>
+          <t>7005336646667.93</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>7346722.397</t>
+          <t>7346722396747.9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12650256.647</t>
+          <t>12650256647199.3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13004972.066</t>
+          <t>13004972065639.3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13232813.204</t>
+          <t>13232813203751.9</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>13270629.119</t>
+          <t>13270629119300.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>13377628.969</t>
+          <t>13377628968757.6</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>13874594.383</t>
+          <t>13874594382606.8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>14237586.366</t>
+          <t>14237586366494.4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>14538115.763</t>
+          <t>14538115762958.7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>15311439.532</t>
+          <t>15311439532364.9</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>16010068.821</t>
+          <t>16010068820911.5</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16545559.338</t>
+          <t>16545559337939.7</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>17423487.366</t>
+          <t>17423487365980.6</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>17724434.091</t>
+          <t>17724434091115</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>18211445.182</t>
+          <t>18211445181621</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>18317903.681</t>
+          <t>18317903681412.6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
